--- a/config/auto_configs/2025_Hyundai_Hyundai_Santa Cruz(NX4A OB)_G 2.5 T-GDI THETA3.xlsx
+++ b/config/auto_configs/2025_Hyundai_Hyundai_Santa Cruz(NX4A OB)_G 2.5 T-GDI THETA3.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="VIN_YMME" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="NWS" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="VIN_YMME" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="NWS" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -492,7 +492,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D195"/>
+  <dimension ref="A1:D257"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -520,17 +520,17 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>ABS/ESC</t>
+          <t>ECM</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>HMA_HK_01548</t>
+          <t>HMA_10697</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>C110913</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -542,17 +542,17 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>ABS/ESC</t>
+          <t>AT</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>HMA_HK_01548</t>
+          <t>HMA_HK_01547</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>C120001</t>
+          <t>P070512</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -564,17 +564,17 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>ABS/ESC</t>
+          <t>AT</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>HMA_HK_01548</t>
+          <t>HMA_HK_01547</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>C120102</t>
+          <t>P070514</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -586,17 +586,17 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>ABS/ESC</t>
+          <t>AT</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>HMA_HK_01548</t>
+          <t>HMA_HK_01547</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>C120202</t>
+          <t>P07051C</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -608,17 +608,17 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>ABS/ESC</t>
+          <t>AT</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>HMA_HK_01548</t>
+          <t>HMA_HK_01547</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>C120301</t>
+          <t>P071200</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -630,17 +630,17 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>ABS/ESC</t>
+          <t>AT</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>HMA_HK_01548</t>
+          <t>HMA_HK_01547</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>C120402</t>
+          <t>P071300</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -652,17 +652,17 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>ABS/ESC</t>
+          <t>AT</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>HMA_HK_01548</t>
+          <t>HMA_HK_01547</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>C120502</t>
+          <t>P072900</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -674,17 +674,17 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>ABS/ESC</t>
+          <t>AT</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>HMA_HK_01548</t>
+          <t>HMA_HK_01547</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>C120601</t>
+          <t>P073000</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -696,17 +696,17 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>ABS/ESC</t>
+          <t>AT</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>HMA_HK_01548</t>
+          <t>HMA_HK_01547</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>C120702</t>
+          <t>P073100</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -718,17 +718,17 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>ABS/ESC</t>
+          <t>AT</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>HMA_HK_01548</t>
+          <t>HMA_HK_01547</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>C120802</t>
+          <t>P073200</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -740,17 +740,17 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>ABS/ESC</t>
+          <t>AT</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>HMA_HK_01548</t>
+          <t>HMA_HK_01547</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>C120901</t>
+          <t>P073300</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -762,17 +762,17 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>ABS/ESC</t>
+          <t>AT</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>HMA_HK_01548</t>
+          <t>HMA_HK_01547</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>C121002</t>
+          <t>P073400</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -784,17 +784,17 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>ABS/ESC</t>
+          <t>AT</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>HMA_HK_01548</t>
+          <t>HMA_HK_01547</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>C121102</t>
+          <t>P073500</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -806,17 +806,17 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>ABS/ESC</t>
+          <t>AT</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>HMA_HK_01548</t>
+          <t>HMA_HK_01547</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>C123501</t>
+          <t>P074100</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -828,17 +828,17 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>ABS/ESC</t>
+          <t>AT</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>HMA_HK_01548</t>
+          <t>HMA_HK_01547</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>C125901</t>
+          <t>P074300</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -850,17 +850,17 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>ABS/ESC</t>
+          <t>AT</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>HMA_HK_01548</t>
+          <t>HMA_HK_01547</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>C126002</t>
+          <t>P074800</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -872,17 +872,17 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>ABS/ESC</t>
+          <t>AT</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>HMA_HK_01548</t>
+          <t>HMA_HK_01547</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>C126104</t>
+          <t>P075300</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -894,17 +894,17 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>ABS/ESC</t>
+          <t>AT</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>HMA_HK_01548</t>
+          <t>HMA_HK_01547</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>C126402</t>
+          <t>P075800</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -916,17 +916,17 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>ABS/ESC</t>
+          <t>AT</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>HMA_HK_01548</t>
+          <t>HMA_HK_01547</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>C128208</t>
+          <t>P076300</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -938,17 +938,17 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>ABS/ESC</t>
+          <t>AT</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>HMA_HK_01548</t>
+          <t>HMA_HK_01547</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>C128302</t>
+          <t>P076800</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -960,17 +960,17 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>ABS/ESC</t>
+          <t>AT</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>HMA_HK_01548</t>
+          <t>HMA_HK_01547</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>C128504</t>
+          <t>P076F00</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -982,17 +982,17 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>ABS/ESC</t>
+          <t>AT</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>HMA_HK_01548</t>
+          <t>HMA_HK_01547</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>C128601</t>
+          <t>P077300</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -1004,17 +1004,17 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>ABS/ESC</t>
+          <t>AT</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>HMA_HK_01548</t>
+          <t>HMA_HK_01547</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>C135801</t>
+          <t>P160200</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -1026,17 +1026,17 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>ABS/ESC</t>
+          <t>AT</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>HMA_HK_01548</t>
+          <t>HMA_HK_01547</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>C137801</t>
+          <t>P270900</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -1048,17 +1048,17 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>ABS/ESC</t>
+          <t>AT</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>HMA_HK_01548</t>
+          <t>HMA_HK_01547</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>C138501</t>
+          <t>U000100</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -1070,17 +1070,17 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>ABS/ESC</t>
+          <t>AT</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>HMA_HK_01548</t>
+          <t>HMA_HK_01547</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>C138602</t>
+          <t>U010000</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -1102,7 +1102,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>C150301</t>
+          <t>C110913</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -1124,7 +1124,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>C152001</t>
+          <t>C120001</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -1146,7 +1146,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>C152601</t>
+          <t>C120102</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -1168,7 +1168,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>C152701</t>
+          <t>C120202</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -1190,7 +1190,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>C161108</t>
+          <t>C120301</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -1212,7 +1212,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>C161208</t>
+          <t>C120402</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -1234,7 +1234,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>C16134A</t>
+          <t>C120502</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -1256,7 +1256,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>C161382</t>
+          <t>C120601</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -1278,7 +1278,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>C161383</t>
+          <t>C120702</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -1300,7 +1300,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>C161386</t>
+          <t>C120802</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -1322,7 +1322,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>C161387</t>
+          <t>C120901</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -1344,7 +1344,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>C162308</t>
+          <t>C121002</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -1366,7 +1366,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>C162708</t>
+          <t>C121102</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -1388,7 +1388,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>C162808</t>
+          <t>C123501</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -1410,7 +1410,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>C162A87</t>
+          <t>C125901</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -1432,7 +1432,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>C162E04</t>
+          <t>C126002</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -1454,7 +1454,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>C162F24</t>
+          <t>C126104</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -1476,7 +1476,7 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>C162F29</t>
+          <t>C126402</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -1498,7 +1498,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>C162F82</t>
+          <t>C128208</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -1520,7 +1520,7 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>C162F83</t>
+          <t>C128302</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
@@ -1542,7 +1542,7 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>C162F87</t>
+          <t>C128504</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
@@ -1564,7 +1564,7 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>C164308</t>
+          <t>C128601</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -1586,7 +1586,7 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>C164683</t>
+          <t>C135801</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
@@ -1608,7 +1608,7 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>C164686</t>
+          <t>C137801</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
@@ -1630,7 +1630,7 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>C164687</t>
+          <t>C138501</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
@@ -1652,7 +1652,7 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>C164808</t>
+          <t>C138602</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
@@ -1674,7 +1674,7 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>C164908</t>
+          <t>C150301</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
@@ -1696,7 +1696,7 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>C165008</t>
+          <t>C152001</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
@@ -1718,7 +1718,7 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>C165687</t>
+          <t>C152601</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
@@ -1740,7 +1740,7 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>C165A87</t>
+          <t>C152701</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
@@ -1762,7 +1762,7 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>C168708</t>
+          <t>C161108</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
@@ -1784,7 +1784,7 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>C169508</t>
+          <t>C161208</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
@@ -1806,7 +1806,7 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>C171004</t>
+          <t>C16134A</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
@@ -1828,7 +1828,7 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>C171055</t>
+          <t>C161382</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
@@ -1850,7 +1850,7 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>C181208</t>
+          <t>C161383</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
@@ -1872,7 +1872,7 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>C183986</t>
+          <t>C161386</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
@@ -1894,7 +1894,7 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>C184787</t>
+          <t>C161387</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
@@ -1916,7 +1916,7 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>C222001</t>
+          <t>C162308</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
@@ -1938,7 +1938,7 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>C222401</t>
+          <t>C162708</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
@@ -1960,7 +1960,7 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>C222808</t>
+          <t>C162808</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
@@ -1982,7 +1982,7 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>C222908</t>
+          <t>C162A87</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
@@ -2004,7 +2004,7 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>C224077</t>
+          <t>C162E04</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
@@ -2026,7 +2026,7 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>C238001</t>
+          <t>C162F24</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
@@ -2048,7 +2048,7 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>C240201</t>
+          <t>C162F29</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
@@ -2070,7 +2070,7 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>C241601</t>
+          <t>C162F82</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
@@ -2092,7 +2092,7 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>C241611</t>
+          <t>C162F83</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
@@ -2114,7 +2114,7 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>C241612</t>
+          <t>C162F87</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
@@ -2136,7 +2136,7 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>C241613</t>
+          <t>C164308</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
@@ -2158,7 +2158,7 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>C241671</t>
+          <t>C164683</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
@@ -2180,7 +2180,7 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>C241701</t>
+          <t>C164686</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
@@ -2202,7 +2202,7 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>C241711</t>
+          <t>C164687</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
@@ -2224,7 +2224,7 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>C241712</t>
+          <t>C164808</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
@@ -2246,7 +2246,7 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>C241713</t>
+          <t>C164908</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
@@ -2268,7 +2268,7 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>C241771</t>
+          <t>C165008</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
@@ -2280,17 +2280,17 @@
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>SRS</t>
+          <t>ABS/ESC</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>HMA_HK_00709</t>
+          <t>HMA_HK_01548</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>B132600</t>
+          <t>C165687</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
@@ -2302,17 +2302,17 @@
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>SRS</t>
+          <t>ABS/ESC</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>HMA_HK_00709</t>
+          <t>HMA_HK_01548</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>B132700</t>
+          <t>C165A87</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
@@ -2324,17 +2324,17 @@
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>SRS</t>
+          <t>ABS/ESC</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>HMA_HK_00709</t>
+          <t>HMA_HK_01548</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>B132800</t>
+          <t>C168708</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
@@ -2346,17 +2346,17 @@
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>SRS</t>
+          <t>ABS/ESC</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>HMA_HK_00709</t>
+          <t>HMA_HK_01548</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>B132900</t>
+          <t>C169508</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
@@ -2368,17 +2368,17 @@
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>SRS</t>
+          <t>ABS/ESC</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>HMA_HK_00709</t>
+          <t>HMA_HK_01548</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>B133000</t>
+          <t>C171004</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
@@ -2390,17 +2390,17 @@
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>SRS</t>
+          <t>ABS/ESC</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>HMA_HK_00709</t>
+          <t>HMA_HK_01548</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>B133100</t>
+          <t>C171055</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
@@ -2412,17 +2412,17 @@
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>SRS</t>
+          <t>ABS/ESC</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>HMA_HK_00709</t>
+          <t>HMA_HK_01548</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>B133200</t>
+          <t>C181208</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
@@ -2434,17 +2434,17 @@
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>SRS</t>
+          <t>ABS/ESC</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>HMA_HK_00709</t>
+          <t>HMA_HK_01548</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>B133300</t>
+          <t>C183986</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
@@ -2456,17 +2456,17 @@
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>SRS</t>
+          <t>ABS/ESC</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>HMA_HK_00709</t>
+          <t>HMA_HK_01548</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>B133400</t>
+          <t>C184787</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
@@ -2478,17 +2478,17 @@
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>SRS</t>
+          <t>ABS/ESC</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>HMA_HK_00709</t>
+          <t>HMA_HK_01548</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>B133500</t>
+          <t>C222001</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
@@ -2500,17 +2500,17 @@
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>SRS</t>
+          <t>ABS/ESC</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>HMA_HK_00709</t>
+          <t>HMA_HK_01548</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>B134600</t>
+          <t>C222401</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
@@ -2522,17 +2522,17 @@
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>SRS</t>
+          <t>ABS/ESC</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>HMA_HK_00709</t>
+          <t>HMA_HK_01548</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>B134700</t>
+          <t>C222808</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
@@ -2544,17 +2544,17 @@
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>SRS</t>
+          <t>ABS/ESC</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>HMA_HK_00709</t>
+          <t>HMA_HK_01548</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>B134800</t>
+          <t>C222908</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
@@ -2566,17 +2566,17 @@
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>SRS</t>
+          <t>ABS/ESC</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>HMA_HK_00709</t>
+          <t>HMA_HK_01548</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>B134900</t>
+          <t>C224077</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
@@ -2588,17 +2588,17 @@
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>SRS</t>
+          <t>ABS/ESC</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>HMA_HK_00709</t>
+          <t>HMA_HK_01548</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>B135200</t>
+          <t>C238001</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
@@ -2610,17 +2610,17 @@
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>SRS</t>
+          <t>ABS/ESC</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>HMA_HK_00709</t>
+          <t>HMA_HK_01548</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>B135300</t>
+          <t>C240201</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
@@ -2632,17 +2632,17 @@
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>SRS</t>
+          <t>ABS/ESC</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>HMA_HK_00709</t>
+          <t>HMA_HK_01548</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>B135400</t>
+          <t>C241601</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
@@ -2654,17 +2654,17 @@
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>SRS</t>
+          <t>ABS/ESC</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>HMA_HK_00709</t>
+          <t>HMA_HK_01548</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>B135500</t>
+          <t>C241611</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
@@ -2676,17 +2676,17 @@
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>SRS</t>
+          <t>ABS/ESC</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>HMA_HK_00709</t>
+          <t>HMA_HK_01548</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>B136100</t>
+          <t>C241612</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
@@ -2698,17 +2698,17 @@
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>SRS</t>
+          <t>ABS/ESC</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>HMA_HK_00709</t>
+          <t>HMA_HK_01548</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>B136200</t>
+          <t>C241613</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
@@ -2720,17 +2720,17 @@
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>SRS</t>
+          <t>ABS/ESC</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>HMA_HK_00709</t>
+          <t>HMA_HK_01548</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>B136300</t>
+          <t>C241671</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
@@ -2742,17 +2742,17 @@
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>SRS</t>
+          <t>ABS/ESC</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>HMA_HK_00709</t>
+          <t>HMA_HK_01548</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>B136400</t>
+          <t>C241701</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
@@ -2764,17 +2764,17 @@
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>SRS</t>
+          <t>ABS/ESC</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>HMA_HK_00709</t>
+          <t>HMA_HK_01548</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>B136700</t>
+          <t>C241711</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
@@ -2786,17 +2786,17 @@
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>SRS</t>
+          <t>ABS/ESC</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>HMA_HK_00709</t>
+          <t>HMA_HK_01548</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>B136800</t>
+          <t>C241712</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
@@ -2808,17 +2808,17 @@
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>SRS</t>
+          <t>ABS/ESC</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>HMA_HK_00709</t>
+          <t>HMA_HK_01548</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>B136900</t>
+          <t>C241713</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
@@ -2830,17 +2830,17 @@
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>SRS</t>
+          <t>ABS/ESC</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>HMA_HK_00709</t>
+          <t>HMA_HK_01548</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>B137000</t>
+          <t>C241771</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
@@ -2857,12 +2857,12 @@
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>HMA_HK_00709</t>
+          <t>HMA_10698</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>B137800</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
@@ -2884,7 +2884,7 @@
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>B137900</t>
+          <t>B132600</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
@@ -2906,7 +2906,7 @@
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>B138000</t>
+          <t>B132700</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
@@ -2928,7 +2928,7 @@
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>B138100</t>
+          <t>B132800</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
@@ -2950,7 +2950,7 @@
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>B138200</t>
+          <t>B132900</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
@@ -2972,7 +2972,7 @@
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>B138300</t>
+          <t>B133000</t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
@@ -2994,7 +2994,7 @@
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>B138400</t>
+          <t>B133100</t>
         </is>
       </c>
       <c r="D114" t="inlineStr">
@@ -3016,7 +3016,7 @@
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>B138500</t>
+          <t>B133200</t>
         </is>
       </c>
       <c r="D115" t="inlineStr">
@@ -3038,7 +3038,7 @@
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>B140000</t>
+          <t>B133300</t>
         </is>
       </c>
       <c r="D116" t="inlineStr">
@@ -3060,7 +3060,7 @@
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>B140100</t>
+          <t>B133400</t>
         </is>
       </c>
       <c r="D117" t="inlineStr">
@@ -3082,7 +3082,7 @@
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>B140200</t>
+          <t>B133500</t>
         </is>
       </c>
       <c r="D118" t="inlineStr">
@@ -3104,7 +3104,7 @@
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>B140300</t>
+          <t>B134600</t>
         </is>
       </c>
       <c r="D119" t="inlineStr">
@@ -3126,7 +3126,7 @@
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>B140400</t>
+          <t>B134700</t>
         </is>
       </c>
       <c r="D120" t="inlineStr">
@@ -3148,7 +3148,7 @@
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>B140500</t>
+          <t>B134800</t>
         </is>
       </c>
       <c r="D121" t="inlineStr">
@@ -3170,7 +3170,7 @@
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>B140900</t>
+          <t>B134900</t>
         </is>
       </c>
       <c r="D122" t="inlineStr">
@@ -3192,7 +3192,7 @@
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>B141000</t>
+          <t>B135200</t>
         </is>
       </c>
       <c r="D123" t="inlineStr">
@@ -3214,7 +3214,7 @@
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>B141200</t>
+          <t>B135300</t>
         </is>
       </c>
       <c r="D124" t="inlineStr">
@@ -3236,7 +3236,7 @@
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>B141300</t>
+          <t>B135400</t>
         </is>
       </c>
       <c r="D125" t="inlineStr">
@@ -3258,7 +3258,7 @@
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>B141400</t>
+          <t>B135500</t>
         </is>
       </c>
       <c r="D126" t="inlineStr">
@@ -3280,7 +3280,7 @@
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>B141500</t>
+          <t>B136100</t>
         </is>
       </c>
       <c r="D127" t="inlineStr">
@@ -3302,7 +3302,7 @@
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>B141600</t>
+          <t>B136200</t>
         </is>
       </c>
       <c r="D128" t="inlineStr">
@@ -3324,7 +3324,7 @@
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>B141700</t>
+          <t>B136300</t>
         </is>
       </c>
       <c r="D129" t="inlineStr">
@@ -3346,7 +3346,7 @@
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>B141800</t>
+          <t>B136400</t>
         </is>
       </c>
       <c r="D130" t="inlineStr">
@@ -3368,7 +3368,7 @@
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>B141900</t>
+          <t>B136700</t>
         </is>
       </c>
       <c r="D131" t="inlineStr">
@@ -3390,7 +3390,7 @@
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>B145100</t>
+          <t>B136800</t>
         </is>
       </c>
       <c r="D132" t="inlineStr">
@@ -3412,7 +3412,7 @@
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>B145200</t>
+          <t>B136900</t>
         </is>
       </c>
       <c r="D133" t="inlineStr">
@@ -3434,7 +3434,7 @@
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>B145400</t>
+          <t>B137000</t>
         </is>
       </c>
       <c r="D134" t="inlineStr">
@@ -3456,7 +3456,7 @@
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>B145500</t>
+          <t>B137800</t>
         </is>
       </c>
       <c r="D135" t="inlineStr">
@@ -3478,7 +3478,7 @@
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>B147300</t>
+          <t>B137900</t>
         </is>
       </c>
       <c r="D136" t="inlineStr">
@@ -3500,7 +3500,7 @@
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>B147400</t>
+          <t>B138000</t>
         </is>
       </c>
       <c r="D137" t="inlineStr">
@@ -3522,7 +3522,7 @@
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>B147500</t>
+          <t>B138100</t>
         </is>
       </c>
       <c r="D138" t="inlineStr">
@@ -3544,7 +3544,7 @@
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>B147600</t>
+          <t>B138200</t>
         </is>
       </c>
       <c r="D139" t="inlineStr">
@@ -3566,7 +3566,7 @@
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>B147700</t>
+          <t>B138300</t>
         </is>
       </c>
       <c r="D140" t="inlineStr">
@@ -3588,7 +3588,7 @@
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>B147800</t>
+          <t>B138400</t>
         </is>
       </c>
       <c r="D141" t="inlineStr">
@@ -3610,7 +3610,7 @@
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>B147900</t>
+          <t>B138500</t>
         </is>
       </c>
       <c r="D142" t="inlineStr">
@@ -3632,7 +3632,7 @@
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>B148000</t>
+          <t>B140000</t>
         </is>
       </c>
       <c r="D143" t="inlineStr">
@@ -3654,7 +3654,7 @@
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>B148100</t>
+          <t>B140100</t>
         </is>
       </c>
       <c r="D144" t="inlineStr">
@@ -3676,7 +3676,7 @@
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>B148200</t>
+          <t>B140200</t>
         </is>
       </c>
       <c r="D145" t="inlineStr">
@@ -3698,7 +3698,7 @@
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>B148300</t>
+          <t>B140300</t>
         </is>
       </c>
       <c r="D146" t="inlineStr">
@@ -3720,7 +3720,7 @@
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>B148400</t>
+          <t>B140400</t>
         </is>
       </c>
       <c r="D147" t="inlineStr">
@@ -3742,7 +3742,7 @@
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>B148500</t>
+          <t>B140500</t>
         </is>
       </c>
       <c r="D148" t="inlineStr">
@@ -3764,7 +3764,7 @@
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>B148600</t>
+          <t>B140900</t>
         </is>
       </c>
       <c r="D149" t="inlineStr">
@@ -3786,7 +3786,7 @@
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>B148700</t>
+          <t>B141000</t>
         </is>
       </c>
       <c r="D150" t="inlineStr">
@@ -3808,7 +3808,7 @@
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>B148800</t>
+          <t>B141200</t>
         </is>
       </c>
       <c r="D151" t="inlineStr">
@@ -3830,7 +3830,7 @@
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>B149000</t>
+          <t>B141300</t>
         </is>
       </c>
       <c r="D152" t="inlineStr">
@@ -3852,7 +3852,7 @@
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t>B149300</t>
+          <t>B141400</t>
         </is>
       </c>
       <c r="D153" t="inlineStr">
@@ -3874,7 +3874,7 @@
       </c>
       <c r="C154" t="inlineStr">
         <is>
-          <t>B149400</t>
+          <t>B141500</t>
         </is>
       </c>
       <c r="D154" t="inlineStr">
@@ -3896,7 +3896,7 @@
       </c>
       <c r="C155" t="inlineStr">
         <is>
-          <t>B151100</t>
+          <t>B141600</t>
         </is>
       </c>
       <c r="D155" t="inlineStr">
@@ -3918,7 +3918,7 @@
       </c>
       <c r="C156" t="inlineStr">
         <is>
-          <t>B151200</t>
+          <t>B141700</t>
         </is>
       </c>
       <c r="D156" t="inlineStr">
@@ -3940,7 +3940,7 @@
       </c>
       <c r="C157" t="inlineStr">
         <is>
-          <t>B151300</t>
+          <t>B141800</t>
         </is>
       </c>
       <c r="D157" t="inlineStr">
@@ -3962,7 +3962,7 @@
       </c>
       <c r="C158" t="inlineStr">
         <is>
-          <t>B151400</t>
+          <t>B141900</t>
         </is>
       </c>
       <c r="D158" t="inlineStr">
@@ -3984,7 +3984,7 @@
       </c>
       <c r="C159" t="inlineStr">
         <is>
-          <t>B151500</t>
+          <t>B145100</t>
         </is>
       </c>
       <c r="D159" t="inlineStr">
@@ -4006,7 +4006,7 @@
       </c>
       <c r="C160" t="inlineStr">
         <is>
-          <t>B151600</t>
+          <t>B145200</t>
         </is>
       </c>
       <c r="D160" t="inlineStr">
@@ -4028,7 +4028,7 @@
       </c>
       <c r="C161" t="inlineStr">
         <is>
-          <t>B162000</t>
+          <t>B145400</t>
         </is>
       </c>
       <c r="D161" t="inlineStr">
@@ -4050,7 +4050,7 @@
       </c>
       <c r="C162" t="inlineStr">
         <is>
-          <t>B165000</t>
+          <t>B145500</t>
         </is>
       </c>
       <c r="D162" t="inlineStr">
@@ -4072,7 +4072,7 @@
       </c>
       <c r="C163" t="inlineStr">
         <is>
-          <t>B165100</t>
+          <t>B147300</t>
         </is>
       </c>
       <c r="D163" t="inlineStr">
@@ -4094,7 +4094,7 @@
       </c>
       <c r="C164" t="inlineStr">
         <is>
-          <t>B165200</t>
+          <t>B147400</t>
         </is>
       </c>
       <c r="D164" t="inlineStr">
@@ -4116,7 +4116,7 @@
       </c>
       <c r="C165" t="inlineStr">
         <is>
-          <t>B165800</t>
+          <t>B147500</t>
         </is>
       </c>
       <c r="D165" t="inlineStr">
@@ -4138,7 +4138,7 @@
       </c>
       <c r="C166" t="inlineStr">
         <is>
-          <t>B167000</t>
+          <t>B147600</t>
         </is>
       </c>
       <c r="D166" t="inlineStr">
@@ -4160,7 +4160,7 @@
       </c>
       <c r="C167" t="inlineStr">
         <is>
-          <t>B167600</t>
+          <t>B147700</t>
         </is>
       </c>
       <c r="D167" t="inlineStr">
@@ -4182,7 +4182,7 @@
       </c>
       <c r="C168" t="inlineStr">
         <is>
-          <t>B167700</t>
+          <t>B147800</t>
         </is>
       </c>
       <c r="D168" t="inlineStr">
@@ -4204,7 +4204,7 @@
       </c>
       <c r="C169" t="inlineStr">
         <is>
-          <t>B167800</t>
+          <t>B147900</t>
         </is>
       </c>
       <c r="D169" t="inlineStr">
@@ -4226,7 +4226,7 @@
       </c>
       <c r="C170" t="inlineStr">
         <is>
-          <t>B168400</t>
+          <t>B148000</t>
         </is>
       </c>
       <c r="D170" t="inlineStr">
@@ -4248,7 +4248,7 @@
       </c>
       <c r="C171" t="inlineStr">
         <is>
-          <t>B16D000</t>
+          <t>B148100</t>
         </is>
       </c>
       <c r="D171" t="inlineStr">
@@ -4270,7 +4270,7 @@
       </c>
       <c r="C172" t="inlineStr">
         <is>
-          <t>B16D100</t>
+          <t>B148200</t>
         </is>
       </c>
       <c r="D172" t="inlineStr">
@@ -4292,7 +4292,7 @@
       </c>
       <c r="C173" t="inlineStr">
         <is>
-          <t>B16D200</t>
+          <t>B148300</t>
         </is>
       </c>
       <c r="D173" t="inlineStr">
@@ -4314,7 +4314,7 @@
       </c>
       <c r="C174" t="inlineStr">
         <is>
-          <t>B16D300</t>
+          <t>B148400</t>
         </is>
       </c>
       <c r="D174" t="inlineStr">
@@ -4336,7 +4336,7 @@
       </c>
       <c r="C175" t="inlineStr">
         <is>
-          <t>B16DC00</t>
+          <t>B148500</t>
         </is>
       </c>
       <c r="D175" t="inlineStr">
@@ -4358,7 +4358,7 @@
       </c>
       <c r="C176" t="inlineStr">
         <is>
-          <t>B173000</t>
+          <t>B148600</t>
         </is>
       </c>
       <c r="D176" t="inlineStr">
@@ -4380,7 +4380,7 @@
       </c>
       <c r="C177" t="inlineStr">
         <is>
-          <t>B173100</t>
+          <t>B148700</t>
         </is>
       </c>
       <c r="D177" t="inlineStr">
@@ -4402,7 +4402,7 @@
       </c>
       <c r="C178" t="inlineStr">
         <is>
-          <t>B173200</t>
+          <t>B148800</t>
         </is>
       </c>
       <c r="D178" t="inlineStr">
@@ -4424,7 +4424,7 @@
       </c>
       <c r="C179" t="inlineStr">
         <is>
-          <t>B173300</t>
+          <t>B149000</t>
         </is>
       </c>
       <c r="D179" t="inlineStr">
@@ -4446,7 +4446,7 @@
       </c>
       <c r="C180" t="inlineStr">
         <is>
-          <t>B173800</t>
+          <t>B149300</t>
         </is>
       </c>
       <c r="D180" t="inlineStr">
@@ -4468,7 +4468,7 @@
       </c>
       <c r="C181" t="inlineStr">
         <is>
-          <t>B173900</t>
+          <t>B149400</t>
         </is>
       </c>
       <c r="D181" t="inlineStr">
@@ -4490,7 +4490,7 @@
       </c>
       <c r="C182" t="inlineStr">
         <is>
-          <t>B174000</t>
+          <t>B151100</t>
         </is>
       </c>
       <c r="D182" t="inlineStr">
@@ -4512,7 +4512,7 @@
       </c>
       <c r="C183" t="inlineStr">
         <is>
-          <t>B174100</t>
+          <t>B151200</t>
         </is>
       </c>
       <c r="D183" t="inlineStr">
@@ -4534,7 +4534,7 @@
       </c>
       <c r="C184" t="inlineStr">
         <is>
-          <t>B174200</t>
+          <t>B151300</t>
         </is>
       </c>
       <c r="D184" t="inlineStr">
@@ -4556,7 +4556,7 @@
       </c>
       <c r="C185" t="inlineStr">
         <is>
-          <t>B174400</t>
+          <t>B151400</t>
         </is>
       </c>
       <c r="D185" t="inlineStr">
@@ -4578,7 +4578,7 @@
       </c>
       <c r="C186" t="inlineStr">
         <is>
-          <t>B174500</t>
+          <t>B151500</t>
         </is>
       </c>
       <c r="D186" t="inlineStr">
@@ -4600,7 +4600,7 @@
       </c>
       <c r="C187" t="inlineStr">
         <is>
-          <t>B174600</t>
+          <t>B151600</t>
         </is>
       </c>
       <c r="D187" t="inlineStr">
@@ -4622,7 +4622,7 @@
       </c>
       <c r="C188" t="inlineStr">
         <is>
-          <t>B174700</t>
+          <t>B162000</t>
         </is>
       </c>
       <c r="D188" t="inlineStr">
@@ -4644,7 +4644,7 @@
       </c>
       <c r="C189" t="inlineStr">
         <is>
-          <t>B174800</t>
+          <t>B165000</t>
         </is>
       </c>
       <c r="D189" t="inlineStr">
@@ -4666,7 +4666,7 @@
       </c>
       <c r="C190" t="inlineStr">
         <is>
-          <t>B176200</t>
+          <t>B165100</t>
         </is>
       </c>
       <c r="D190" t="inlineStr">
@@ -4688,7 +4688,7 @@
       </c>
       <c r="C191" t="inlineStr">
         <is>
-          <t>B250200</t>
+          <t>B165200</t>
         </is>
       </c>
       <c r="D191" t="inlineStr">
@@ -4710,7 +4710,7 @@
       </c>
       <c r="C192" t="inlineStr">
         <is>
-          <t>B261300</t>
+          <t>B165800</t>
         </is>
       </c>
       <c r="D192" t="inlineStr">
@@ -4732,7 +4732,7 @@
       </c>
       <c r="C193" t="inlineStr">
         <is>
-          <t>B261500</t>
+          <t>B167000</t>
         </is>
       </c>
       <c r="D193" t="inlineStr">
@@ -4754,7 +4754,7 @@
       </c>
       <c r="C194" t="inlineStr">
         <is>
-          <t>B261600</t>
+          <t>B167600</t>
         </is>
       </c>
       <c r="D194" t="inlineStr">
@@ -4771,15 +4771,1379 @@
       </c>
       <c r="B195" t="inlineStr">
         <is>
-          <t>HMA_10698</t>
+          <t>HMA_HK_00709</t>
         </is>
       </c>
       <c r="C195" t="inlineStr">
         <is>
+          <t>B167700</t>
+        </is>
+      </c>
+      <c r="D195" t="inlineStr">
+        <is>
+          <t>00</t>
+        </is>
+      </c>
+    </row>
+    <row r="196">
+      <c r="A196" t="inlineStr">
+        <is>
+          <t>SRS</t>
+        </is>
+      </c>
+      <c r="B196" t="inlineStr">
+        <is>
+          <t>HMA_HK_00709</t>
+        </is>
+      </c>
+      <c r="C196" t="inlineStr">
+        <is>
+          <t>B167800</t>
+        </is>
+      </c>
+      <c r="D196" t="inlineStr">
+        <is>
+          <t>00</t>
+        </is>
+      </c>
+    </row>
+    <row r="197">
+      <c r="A197" t="inlineStr">
+        <is>
+          <t>SRS</t>
+        </is>
+      </c>
+      <c r="B197" t="inlineStr">
+        <is>
+          <t>HMA_HK_00709</t>
+        </is>
+      </c>
+      <c r="C197" t="inlineStr">
+        <is>
+          <t>B168400</t>
+        </is>
+      </c>
+      <c r="D197" t="inlineStr">
+        <is>
+          <t>00</t>
+        </is>
+      </c>
+    </row>
+    <row r="198">
+      <c r="A198" t="inlineStr">
+        <is>
+          <t>SRS</t>
+        </is>
+      </c>
+      <c r="B198" t="inlineStr">
+        <is>
+          <t>HMA_HK_00709</t>
+        </is>
+      </c>
+      <c r="C198" t="inlineStr">
+        <is>
+          <t>B16D000</t>
+        </is>
+      </c>
+      <c r="D198" t="inlineStr">
+        <is>
+          <t>00</t>
+        </is>
+      </c>
+    </row>
+    <row r="199">
+      <c r="A199" t="inlineStr">
+        <is>
+          <t>SRS</t>
+        </is>
+      </c>
+      <c r="B199" t="inlineStr">
+        <is>
+          <t>HMA_HK_00709</t>
+        </is>
+      </c>
+      <c r="C199" t="inlineStr">
+        <is>
+          <t>B16D100</t>
+        </is>
+      </c>
+      <c r="D199" t="inlineStr">
+        <is>
+          <t>00</t>
+        </is>
+      </c>
+    </row>
+    <row r="200">
+      <c r="A200" t="inlineStr">
+        <is>
+          <t>SRS</t>
+        </is>
+      </c>
+      <c r="B200" t="inlineStr">
+        <is>
+          <t>HMA_HK_00709</t>
+        </is>
+      </c>
+      <c r="C200" t="inlineStr">
+        <is>
+          <t>B16D200</t>
+        </is>
+      </c>
+      <c r="D200" t="inlineStr">
+        <is>
+          <t>00</t>
+        </is>
+      </c>
+    </row>
+    <row r="201">
+      <c r="A201" t="inlineStr">
+        <is>
+          <t>SRS</t>
+        </is>
+      </c>
+      <c r="B201" t="inlineStr">
+        <is>
+          <t>HMA_HK_00709</t>
+        </is>
+      </c>
+      <c r="C201" t="inlineStr">
+        <is>
+          <t>B16D300</t>
+        </is>
+      </c>
+      <c r="D201" t="inlineStr">
+        <is>
+          <t>00</t>
+        </is>
+      </c>
+    </row>
+    <row r="202">
+      <c r="A202" t="inlineStr">
+        <is>
+          <t>SRS</t>
+        </is>
+      </c>
+      <c r="B202" t="inlineStr">
+        <is>
+          <t>HMA_HK_00709</t>
+        </is>
+      </c>
+      <c r="C202" t="inlineStr">
+        <is>
+          <t>B16DC00</t>
+        </is>
+      </c>
+      <c r="D202" t="inlineStr">
+        <is>
+          <t>00</t>
+        </is>
+      </c>
+    </row>
+    <row r="203">
+      <c r="A203" t="inlineStr">
+        <is>
+          <t>SRS</t>
+        </is>
+      </c>
+      <c r="B203" t="inlineStr">
+        <is>
+          <t>HMA_HK_00709</t>
+        </is>
+      </c>
+      <c r="C203" t="inlineStr">
+        <is>
+          <t>B173000</t>
+        </is>
+      </c>
+      <c r="D203" t="inlineStr">
+        <is>
+          <t>00</t>
+        </is>
+      </c>
+    </row>
+    <row r="204">
+      <c r="A204" t="inlineStr">
+        <is>
+          <t>SRS</t>
+        </is>
+      </c>
+      <c r="B204" t="inlineStr">
+        <is>
+          <t>HMA_HK_00709</t>
+        </is>
+      </c>
+      <c r="C204" t="inlineStr">
+        <is>
+          <t>B173100</t>
+        </is>
+      </c>
+      <c r="D204" t="inlineStr">
+        <is>
+          <t>00</t>
+        </is>
+      </c>
+    </row>
+    <row r="205">
+      <c r="A205" t="inlineStr">
+        <is>
+          <t>SRS</t>
+        </is>
+      </c>
+      <c r="B205" t="inlineStr">
+        <is>
+          <t>HMA_HK_00709</t>
+        </is>
+      </c>
+      <c r="C205" t="inlineStr">
+        <is>
+          <t>B173200</t>
+        </is>
+      </c>
+      <c r="D205" t="inlineStr">
+        <is>
+          <t>00</t>
+        </is>
+      </c>
+    </row>
+    <row r="206">
+      <c r="A206" t="inlineStr">
+        <is>
+          <t>SRS</t>
+        </is>
+      </c>
+      <c r="B206" t="inlineStr">
+        <is>
+          <t>HMA_HK_00709</t>
+        </is>
+      </c>
+      <c r="C206" t="inlineStr">
+        <is>
+          <t>B173300</t>
+        </is>
+      </c>
+      <c r="D206" t="inlineStr">
+        <is>
+          <t>00</t>
+        </is>
+      </c>
+    </row>
+    <row r="207">
+      <c r="A207" t="inlineStr">
+        <is>
+          <t>SRS</t>
+        </is>
+      </c>
+      <c r="B207" t="inlineStr">
+        <is>
+          <t>HMA_HK_00709</t>
+        </is>
+      </c>
+      <c r="C207" t="inlineStr">
+        <is>
+          <t>B173800</t>
+        </is>
+      </c>
+      <c r="D207" t="inlineStr">
+        <is>
+          <t>00</t>
+        </is>
+      </c>
+    </row>
+    <row r="208">
+      <c r="A208" t="inlineStr">
+        <is>
+          <t>SRS</t>
+        </is>
+      </c>
+      <c r="B208" t="inlineStr">
+        <is>
+          <t>HMA_HK_00709</t>
+        </is>
+      </c>
+      <c r="C208" t="inlineStr">
+        <is>
+          <t>B173900</t>
+        </is>
+      </c>
+      <c r="D208" t="inlineStr">
+        <is>
+          <t>00</t>
+        </is>
+      </c>
+    </row>
+    <row r="209">
+      <c r="A209" t="inlineStr">
+        <is>
+          <t>SRS</t>
+        </is>
+      </c>
+      <c r="B209" t="inlineStr">
+        <is>
+          <t>HMA_HK_00709</t>
+        </is>
+      </c>
+      <c r="C209" t="inlineStr">
+        <is>
+          <t>B174000</t>
+        </is>
+      </c>
+      <c r="D209" t="inlineStr">
+        <is>
+          <t>00</t>
+        </is>
+      </c>
+    </row>
+    <row r="210">
+      <c r="A210" t="inlineStr">
+        <is>
+          <t>SRS</t>
+        </is>
+      </c>
+      <c r="B210" t="inlineStr">
+        <is>
+          <t>HMA_HK_00709</t>
+        </is>
+      </c>
+      <c r="C210" t="inlineStr">
+        <is>
+          <t>B174100</t>
+        </is>
+      </c>
+      <c r="D210" t="inlineStr">
+        <is>
+          <t>00</t>
+        </is>
+      </c>
+    </row>
+    <row r="211">
+      <c r="A211" t="inlineStr">
+        <is>
+          <t>SRS</t>
+        </is>
+      </c>
+      <c r="B211" t="inlineStr">
+        <is>
+          <t>HMA_HK_00709</t>
+        </is>
+      </c>
+      <c r="C211" t="inlineStr">
+        <is>
+          <t>B174200</t>
+        </is>
+      </c>
+      <c r="D211" t="inlineStr">
+        <is>
+          <t>00</t>
+        </is>
+      </c>
+    </row>
+    <row r="212">
+      <c r="A212" t="inlineStr">
+        <is>
+          <t>SRS</t>
+        </is>
+      </c>
+      <c r="B212" t="inlineStr">
+        <is>
+          <t>HMA_HK_00709</t>
+        </is>
+      </c>
+      <c r="C212" t="inlineStr">
+        <is>
+          <t>B174400</t>
+        </is>
+      </c>
+      <c r="D212" t="inlineStr">
+        <is>
+          <t>00</t>
+        </is>
+      </c>
+    </row>
+    <row r="213">
+      <c r="A213" t="inlineStr">
+        <is>
+          <t>SRS</t>
+        </is>
+      </c>
+      <c r="B213" t="inlineStr">
+        <is>
+          <t>HMA_HK_00709</t>
+        </is>
+      </c>
+      <c r="C213" t="inlineStr">
+        <is>
+          <t>B174500</t>
+        </is>
+      </c>
+      <c r="D213" t="inlineStr">
+        <is>
+          <t>00</t>
+        </is>
+      </c>
+    </row>
+    <row r="214">
+      <c r="A214" t="inlineStr">
+        <is>
+          <t>SRS</t>
+        </is>
+      </c>
+      <c r="B214" t="inlineStr">
+        <is>
+          <t>HMA_HK_00709</t>
+        </is>
+      </c>
+      <c r="C214" t="inlineStr">
+        <is>
+          <t>B174600</t>
+        </is>
+      </c>
+      <c r="D214" t="inlineStr">
+        <is>
+          <t>00</t>
+        </is>
+      </c>
+    </row>
+    <row r="215">
+      <c r="A215" t="inlineStr">
+        <is>
+          <t>SRS</t>
+        </is>
+      </c>
+      <c r="B215" t="inlineStr">
+        <is>
+          <t>HMA_HK_00709</t>
+        </is>
+      </c>
+      <c r="C215" t="inlineStr">
+        <is>
+          <t>B174700</t>
+        </is>
+      </c>
+      <c r="D215" t="inlineStr">
+        <is>
+          <t>00</t>
+        </is>
+      </c>
+    </row>
+    <row r="216">
+      <c r="A216" t="inlineStr">
+        <is>
+          <t>SRS</t>
+        </is>
+      </c>
+      <c r="B216" t="inlineStr">
+        <is>
+          <t>HMA_HK_00709</t>
+        </is>
+      </c>
+      <c r="C216" t="inlineStr">
+        <is>
+          <t>B174800</t>
+        </is>
+      </c>
+      <c r="D216" t="inlineStr">
+        <is>
+          <t>00</t>
+        </is>
+      </c>
+    </row>
+    <row r="217">
+      <c r="A217" t="inlineStr">
+        <is>
+          <t>SRS</t>
+        </is>
+      </c>
+      <c r="B217" t="inlineStr">
+        <is>
+          <t>HMA_HK_00709</t>
+        </is>
+      </c>
+      <c r="C217" t="inlineStr">
+        <is>
+          <t>B176200</t>
+        </is>
+      </c>
+      <c r="D217" t="inlineStr">
+        <is>
+          <t>00</t>
+        </is>
+      </c>
+    </row>
+    <row r="218">
+      <c r="A218" t="inlineStr">
+        <is>
+          <t>SRS</t>
+        </is>
+      </c>
+      <c r="B218" t="inlineStr">
+        <is>
+          <t>HMA_HK_00709</t>
+        </is>
+      </c>
+      <c r="C218" t="inlineStr">
+        <is>
+          <t>B250200</t>
+        </is>
+      </c>
+      <c r="D218" t="inlineStr">
+        <is>
+          <t>00</t>
+        </is>
+      </c>
+    </row>
+    <row r="219">
+      <c r="A219" t="inlineStr">
+        <is>
+          <t>SRS</t>
+        </is>
+      </c>
+      <c r="B219" t="inlineStr">
+        <is>
+          <t>HMA_HK_00709</t>
+        </is>
+      </c>
+      <c r="C219" t="inlineStr">
+        <is>
+          <t>B261300</t>
+        </is>
+      </c>
+      <c r="D219" t="inlineStr">
+        <is>
+          <t>00</t>
+        </is>
+      </c>
+    </row>
+    <row r="220">
+      <c r="A220" t="inlineStr">
+        <is>
+          <t>SRS</t>
+        </is>
+      </c>
+      <c r="B220" t="inlineStr">
+        <is>
+          <t>HMA_HK_00709</t>
+        </is>
+      </c>
+      <c r="C220" t="inlineStr">
+        <is>
+          <t>B261500</t>
+        </is>
+      </c>
+      <c r="D220" t="inlineStr">
+        <is>
+          <t>00</t>
+        </is>
+      </c>
+    </row>
+    <row r="221">
+      <c r="A221" t="inlineStr">
+        <is>
+          <t>SRS</t>
+        </is>
+      </c>
+      <c r="B221" t="inlineStr">
+        <is>
+          <t>HMA_HK_00709</t>
+        </is>
+      </c>
+      <c r="C221" t="inlineStr">
+        <is>
+          <t>B261600</t>
+        </is>
+      </c>
+      <c r="D221" t="inlineStr">
+        <is>
+          <t>00</t>
+        </is>
+      </c>
+    </row>
+    <row r="222">
+      <c r="A222" t="inlineStr">
+        <is>
+          <t>BDC-TPMS</t>
+        </is>
+      </c>
+      <c r="B222" t="inlineStr">
+        <is>
+          <t>HMA_10626</t>
+        </is>
+      </c>
+      <c r="C222" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="D195" t="inlineStr">
+      <c r="D222" t="inlineStr">
+        <is>
+          <t>00</t>
+        </is>
+      </c>
+    </row>
+    <row r="223">
+      <c r="A223" t="inlineStr">
+        <is>
+          <t>4WD</t>
+        </is>
+      </c>
+      <c r="B223" t="inlineStr">
+        <is>
+          <t>HMA_HK_00712</t>
+        </is>
+      </c>
+      <c r="C223" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D223" t="inlineStr">
+        <is>
+          <t>00</t>
+        </is>
+      </c>
+    </row>
+    <row r="224">
+      <c r="A224" t="inlineStr">
+        <is>
+          <t>A/C</t>
+        </is>
+      </c>
+      <c r="B224" t="inlineStr">
+        <is>
+          <t>HMA_10607</t>
+        </is>
+      </c>
+      <c r="C224" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D224" t="inlineStr">
+        <is>
+          <t>00</t>
+        </is>
+      </c>
+    </row>
+    <row r="225">
+      <c r="A225" t="inlineStr">
+        <is>
+          <t>ADAS_P</t>
+        </is>
+      </c>
+      <c r="B225" t="inlineStr">
+        <is>
+          <t>HMA_10629</t>
+        </is>
+      </c>
+      <c r="C225" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D225" t="inlineStr">
+        <is>
+          <t>00</t>
+        </is>
+      </c>
+    </row>
+    <row r="226">
+      <c r="A226" t="inlineStr">
+        <is>
+          <t>ADAS_P</t>
+        </is>
+      </c>
+      <c r="B226" t="inlineStr">
+        <is>
+          <t>HMA_10630</t>
+        </is>
+      </c>
+      <c r="C226" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D226" t="inlineStr">
+        <is>
+          <t>00</t>
+        </is>
+      </c>
+    </row>
+    <row r="227">
+      <c r="A227" t="inlineStr">
+        <is>
+          <t>AMP</t>
+        </is>
+      </c>
+      <c r="B227" t="inlineStr">
+        <is>
+          <t>HMA_10611</t>
+        </is>
+      </c>
+      <c r="C227" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D227" t="inlineStr">
+        <is>
+          <t>00</t>
+        </is>
+      </c>
+    </row>
+    <row r="228">
+      <c r="A228" t="inlineStr">
+        <is>
+          <t>BDC-BCM</t>
+        </is>
+      </c>
+      <c r="B228" t="inlineStr">
+        <is>
+          <t>HMA_10622</t>
+        </is>
+      </c>
+      <c r="C228" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D228" t="inlineStr">
+        <is>
+          <t>00</t>
+        </is>
+      </c>
+    </row>
+    <row r="229">
+      <c r="A229" t="inlineStr">
+        <is>
+          <t>BDC-IAU</t>
+        </is>
+      </c>
+      <c r="B229" t="inlineStr">
+        <is>
+          <t>HMA_10624</t>
+        </is>
+      </c>
+      <c r="C229" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D229" t="inlineStr">
+        <is>
+          <t>00</t>
+        </is>
+      </c>
+    </row>
+    <row r="230">
+      <c r="A230" t="inlineStr">
+        <is>
+          <t>BDC-IMM</t>
+        </is>
+      </c>
+      <c r="B230" t="inlineStr">
+        <is>
+          <t>HMA_10623</t>
+        </is>
+      </c>
+      <c r="C230" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D230" t="inlineStr">
+        <is>
+          <t>00</t>
+        </is>
+      </c>
+    </row>
+    <row r="231">
+      <c r="A231" t="inlineStr">
+        <is>
+          <t>BDC-SKU</t>
+        </is>
+      </c>
+      <c r="B231" t="inlineStr">
+        <is>
+          <t>HMA_10625</t>
+        </is>
+      </c>
+      <c r="C231" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D231" t="inlineStr">
+        <is>
+          <t>00</t>
+        </is>
+      </c>
+    </row>
+    <row r="232">
+      <c r="A232" t="inlineStr">
+        <is>
+          <t>CCNC</t>
+        </is>
+      </c>
+      <c r="B232" t="inlineStr">
+        <is>
+          <t>HMA_10621</t>
+        </is>
+      </c>
+      <c r="C232" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D232" t="inlineStr">
+        <is>
+          <t>00</t>
+        </is>
+      </c>
+    </row>
+    <row r="233">
+      <c r="A233" t="inlineStr">
+        <is>
+          <t>CCU_CCNF</t>
+        </is>
+      </c>
+      <c r="B233" t="inlineStr">
+        <is>
+          <t>HMA_10618</t>
+        </is>
+      </c>
+      <c r="C233" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D233" t="inlineStr">
+        <is>
+          <t>00</t>
+        </is>
+      </c>
+    </row>
+    <row r="234">
+      <c r="A234" t="inlineStr">
+        <is>
+          <t>CCU_CGW</t>
+        </is>
+      </c>
+      <c r="B234" t="inlineStr">
+        <is>
+          <t>HMA_10619</t>
+        </is>
+      </c>
+      <c r="C234" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D234" t="inlineStr">
+        <is>
+          <t>00</t>
+        </is>
+      </c>
+    </row>
+    <row r="235">
+      <c r="A235" t="inlineStr">
+        <is>
+          <t>CLU</t>
+        </is>
+      </c>
+      <c r="B235" t="inlineStr">
+        <is>
+          <t>HMA_HK_01557</t>
+        </is>
+      </c>
+      <c r="C235" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D235" t="inlineStr">
+        <is>
+          <t>00</t>
+        </is>
+      </c>
+    </row>
+    <row r="236">
+      <c r="A236" t="inlineStr">
+        <is>
+          <t>DAU</t>
+        </is>
+      </c>
+      <c r="B236" t="inlineStr">
+        <is>
+          <t>HMA_10614</t>
+        </is>
+      </c>
+      <c r="C236" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D236" t="inlineStr">
+        <is>
+          <t>00</t>
+        </is>
+      </c>
+    </row>
+    <row r="237">
+      <c r="A237" t="inlineStr">
+        <is>
+          <t>DCU</t>
+        </is>
+      </c>
+      <c r="B237" t="inlineStr">
+        <is>
+          <t>HMA_10620</t>
+        </is>
+      </c>
+      <c r="C237" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D237" t="inlineStr">
+        <is>
+          <t>00</t>
+        </is>
+      </c>
+    </row>
+    <row r="238">
+      <c r="A238" t="inlineStr">
+        <is>
+          <t>DHS_FL</t>
+        </is>
+      </c>
+      <c r="B238" t="inlineStr">
+        <is>
+          <t>HMA_10615</t>
+        </is>
+      </c>
+      <c r="C238" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D238" t="inlineStr">
+        <is>
+          <t>00</t>
+        </is>
+      </c>
+    </row>
+    <row r="239">
+      <c r="A239" t="inlineStr">
+        <is>
+          <t>DHS_FR</t>
+        </is>
+      </c>
+      <c r="B239" t="inlineStr">
+        <is>
+          <t>HMA_10616</t>
+        </is>
+      </c>
+      <c r="C239" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D239" t="inlineStr">
+        <is>
+          <t>00</t>
+        </is>
+      </c>
+    </row>
+    <row r="240">
+      <c r="A240" t="inlineStr">
+        <is>
+          <t>EPS</t>
+        </is>
+      </c>
+      <c r="B240" t="inlineStr">
+        <is>
+          <t>HMA_HK_01018</t>
+        </is>
+      </c>
+      <c r="C240" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D240" t="inlineStr">
+        <is>
+          <t>00</t>
+        </is>
+      </c>
+    </row>
+    <row r="241">
+      <c r="A241" t="inlineStr">
+        <is>
+          <t>FPM</t>
+        </is>
+      </c>
+      <c r="B241" t="inlineStr">
+        <is>
+          <t>HMA_10633</t>
+        </is>
+      </c>
+      <c r="C241" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D241" t="inlineStr">
+        <is>
+          <t>00</t>
+        </is>
+      </c>
+    </row>
+    <row r="242">
+      <c r="A242" t="inlineStr">
+        <is>
+          <t>FR</t>
+        </is>
+      </c>
+      <c r="B242" t="inlineStr">
+        <is>
+          <t>HMA_HK_01559</t>
+        </is>
+      </c>
+      <c r="C242" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D242" t="inlineStr">
+        <is>
+          <t>00</t>
+        </is>
+      </c>
+    </row>
+    <row r="243">
+      <c r="A243" t="inlineStr">
+        <is>
+          <t>FVC</t>
+        </is>
+      </c>
+      <c r="B243" t="inlineStr">
+        <is>
+          <t>HMA_HK_01560</t>
+        </is>
+      </c>
+      <c r="C243" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D243" t="inlineStr">
+        <is>
+          <t>00</t>
+        </is>
+      </c>
+    </row>
+    <row r="244">
+      <c r="A244" t="inlineStr">
+        <is>
+          <t>ICC</t>
+        </is>
+      </c>
+      <c r="B244" t="inlineStr">
+        <is>
+          <t>HMA_10617</t>
+        </is>
+      </c>
+      <c r="C244" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D244" t="inlineStr">
+        <is>
+          <t>00</t>
+        </is>
+      </c>
+    </row>
+    <row r="245">
+      <c r="A245" t="inlineStr">
+        <is>
+          <t>MKBD</t>
+        </is>
+      </c>
+      <c r="B245" t="inlineStr">
+        <is>
+          <t>HMA_10628</t>
+        </is>
+      </c>
+      <c r="C245" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D245" t="inlineStr">
+        <is>
+          <t>00</t>
+        </is>
+      </c>
+    </row>
+    <row r="246">
+      <c r="A246" t="inlineStr">
+        <is>
+          <t>MLM</t>
+        </is>
+      </c>
+      <c r="B246" t="inlineStr">
+        <is>
+          <t>HMA_10612</t>
+        </is>
+      </c>
+      <c r="C246" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D246" t="inlineStr">
+        <is>
+          <t>00</t>
+        </is>
+      </c>
+    </row>
+    <row r="247">
+      <c r="A247" t="inlineStr">
+        <is>
+          <t>OCS</t>
+        </is>
+      </c>
+      <c r="B247" t="inlineStr">
+        <is>
+          <t>HMA_10610</t>
+        </is>
+      </c>
+      <c r="C247" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D247" t="inlineStr">
+        <is>
+          <t>00</t>
+        </is>
+      </c>
+    </row>
+    <row r="248">
+      <c r="A248" t="inlineStr">
+        <is>
+          <t>P_LBM</t>
+        </is>
+      </c>
+      <c r="B248" t="inlineStr">
+        <is>
+          <t>HMA_10631</t>
+        </is>
+      </c>
+      <c r="C248" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D248" t="inlineStr">
+        <is>
+          <t>00</t>
+        </is>
+      </c>
+    </row>
+    <row r="249">
+      <c r="A249" t="inlineStr">
+        <is>
+          <t>PDC</t>
+        </is>
+      </c>
+      <c r="B249" t="inlineStr">
+        <is>
+          <t>HMA_10627</t>
+        </is>
+      </c>
+      <c r="C249" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D249" t="inlineStr">
+        <is>
+          <t>00</t>
+        </is>
+      </c>
+    </row>
+    <row r="250">
+      <c r="A250" t="inlineStr">
+        <is>
+          <t>PDCE</t>
+        </is>
+      </c>
+      <c r="B250" t="inlineStr">
+        <is>
+          <t>HMA_10632</t>
+        </is>
+      </c>
+      <c r="C250" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D250" t="inlineStr">
+        <is>
+          <t>00</t>
+        </is>
+      </c>
+    </row>
+    <row r="251">
+      <c r="A251" t="inlineStr">
+        <is>
+          <t>PSM</t>
+        </is>
+      </c>
+      <c r="B251" t="inlineStr">
+        <is>
+          <t>HMA_10608</t>
+        </is>
+      </c>
+      <c r="C251" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D251" t="inlineStr">
+        <is>
+          <t>00</t>
+        </is>
+      </c>
+    </row>
+    <row r="252">
+      <c r="A252" t="inlineStr">
+        <is>
+          <t>RCR-L</t>
+        </is>
+      </c>
+      <c r="B252" t="inlineStr">
+        <is>
+          <t>HMA_HK_01567</t>
+        </is>
+      </c>
+      <c r="C252" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D252" t="inlineStr">
+        <is>
+          <t>00</t>
+        </is>
+      </c>
+    </row>
+    <row r="253">
+      <c r="A253" t="inlineStr">
+        <is>
+          <t>RCR-R</t>
+        </is>
+      </c>
+      <c r="B253" t="inlineStr">
+        <is>
+          <t>HMA_HK_01568</t>
+        </is>
+      </c>
+      <c r="C253" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D253" t="inlineStr">
+        <is>
+          <t>00</t>
+        </is>
+      </c>
+    </row>
+    <row r="254">
+      <c r="A254" t="inlineStr">
+        <is>
+          <t>SHVU-F</t>
+        </is>
+      </c>
+      <c r="B254" t="inlineStr">
+        <is>
+          <t>HMA_HK_01570</t>
+        </is>
+      </c>
+      <c r="C254" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D254" t="inlineStr">
+        <is>
+          <t>00</t>
+        </is>
+      </c>
+    </row>
+    <row r="255">
+      <c r="A255" t="inlineStr">
+        <is>
+          <t>SHVU-R</t>
+        </is>
+      </c>
+      <c r="B255" t="inlineStr">
+        <is>
+          <t>HMA_10613</t>
+        </is>
+      </c>
+      <c r="C255" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D255" t="inlineStr">
+        <is>
+          <t>00</t>
+        </is>
+      </c>
+    </row>
+    <row r="256">
+      <c r="A256" t="inlineStr">
+        <is>
+          <t>SWRC</t>
+        </is>
+      </c>
+      <c r="B256" t="inlineStr">
+        <is>
+          <t>HMA_10609</t>
+        </is>
+      </c>
+      <c r="C256" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D256" t="inlineStr">
+        <is>
+          <t>00</t>
+        </is>
+      </c>
+    </row>
+    <row r="257">
+      <c r="A257" t="inlineStr">
+        <is>
+          <t>WPC</t>
+        </is>
+      </c>
+      <c r="B257" t="inlineStr">
+        <is>
+          <t>HMA_HK_00759</t>
+        </is>
+      </c>
+      <c r="C257" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D257" t="inlineStr">
         <is>
           <t>00</t>
         </is>
